--- a/outputs/283-32.xlsx
+++ b/outputs/283-32.xlsx
@@ -341,80 +341,84 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="5" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="2" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -610,605 +614,605 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="2.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="8"/>
+      <c r="D8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="A9" s="11" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13" t="n">
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="14" t="n">
         <v>2743626.43</v>
       </c>
-      <c r="G9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="13" t="n">
+      <c r="F10" s="15"/>
+      <c r="G10" s="14" t="n">
         <v>19800</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="13" t="n">
+      <c r="F11" s="15"/>
+      <c r="G11" s="14" t="n">
         <v>99000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="13" t="n">
+      <c r="F12" s="15"/>
+      <c r="G12" s="14" t="n">
         <v>908010</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="13" t="n">
+      <c r="F13" s="15"/>
+      <c r="G13" s="14" t="n">
         <v>13680</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="13" t="n">
+      <c r="F14" s="15"/>
+      <c r="G14" s="14" t="n">
         <v>130500</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="A15" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="13" t="n">
+      <c r="F15" s="15"/>
+      <c r="G15" s="14" t="n">
         <v>27720</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="13" t="n">
+      <c r="F16" s="15"/>
+      <c r="G16" s="14" t="n">
         <v>154800</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B17" s="11" t="s">
+      <c r="A17" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="13" t="n">
+      <c r="F17" s="15"/>
+      <c r="G17" s="14" t="n">
         <v>153000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="A18" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="18" t="s">
+      <c r="D18" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="14" t="n">
         <v>1525.42</v>
       </c>
-      <c r="G18" s="14"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="A19" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="18" t="s">
+      <c r="D19" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="14" t="n">
         <v>36610.17</v>
       </c>
-      <c r="G19" s="14"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="A20" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="18" t="s">
+      <c r="D20" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="14" t="n">
         <v>113491.53</v>
       </c>
-      <c r="G20" s="14"/>
+      <c r="G20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="A21" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="18" t="s">
+      <c r="D21" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="14" t="n">
         <v>34322.03</v>
       </c>
-      <c r="G21" s="14"/>
+      <c r="G21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="18" t="s">
+      <c r="D22" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="14" t="n">
         <v>5033.9</v>
       </c>
-      <c r="G22" s="14"/>
+      <c r="G22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="18" t="s">
+      <c r="D23" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="14" t="n">
         <v>1952.54</v>
       </c>
-      <c r="G23" s="14"/>
+      <c r="G23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="A24" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="18" t="s">
+      <c r="D24" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="14" t="n">
         <v>381.36</v>
       </c>
-      <c r="G24" s="14"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="A25" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="14" t="n">
         <v>152.46</v>
       </c>
-      <c r="G25" s="14"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="A26" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="14" t="n">
         <v>152.46</v>
       </c>
-      <c r="G26" s="14"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="A27" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="14" t="n">
         <v>1525.42</v>
       </c>
-      <c r="G27" s="14"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="16" t="s">
+      <c r="A28" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="13" t="n">
+      <c r="E28" s="19"/>
+      <c r="F28" s="14" t="n">
         <v>1800</v>
       </c>
-      <c r="G28" s="14"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="16" t="s">
+      <c r="A29" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="18" t="s">
+      <c r="D29" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="14" t="n">
         <v>1220.34</v>
       </c>
-      <c r="G29" s="14"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="A30" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="18" t="s">
+      <c r="D30" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="14" t="n">
         <v>2181.36</v>
       </c>
-      <c r="G30" s="14"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="A31" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="18" t="s">
+      <c r="D31" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="14" t="n">
         <v>6864.41</v>
       </c>
-      <c r="G31" s="14"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="A32" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="18" t="s">
+      <c r="D32" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="14" t="n">
         <v>6864.41</v>
       </c>
-      <c r="G32" s="14"/>
+      <c r="G32" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1240,605 +1244,605 @@
   <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="2.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="A5" s="6"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="A6" s="6"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8" t="s">
+      <c r="C8" s="8"/>
+      <c r="D8" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="F8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="10" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B9" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="A9" s="11" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="13" t="n">
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="14" t="n">
         <v>2743626.43</v>
       </c>
-      <c r="G9" s="14"/>
+      <c r="G9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B10" s="11" t="s">
+      <c r="A10" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="13" t="n">
+      <c r="F10" s="15"/>
+      <c r="G10" s="14" t="n">
         <v>19800</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B11" s="11" t="s">
+      <c r="A11" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B11" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="16" t="s">
+      <c r="C11" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="D11" s="17" t="s">
+      <c r="D11" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="13" t="n">
+      <c r="F11" s="15"/>
+      <c r="G11" s="14" t="n">
         <v>99000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B12" s="11" t="s">
+      <c r="A12" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B12" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="17" t="s">
+      <c r="D12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="13" t="n">
+      <c r="F12" s="15"/>
+      <c r="G12" s="14" t="n">
         <v>13680</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B13" s="11" t="s">
+      <c r="A13" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="16" t="s">
+      <c r="C13" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="17" t="s">
+      <c r="D13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="F13" s="14"/>
-      <c r="G13" s="13" t="n">
+      <c r="F13" s="15"/>
+      <c r="G13" s="14" t="n">
         <v>130500</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B14" s="11" t="s">
+      <c r="A14" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="16" t="s">
+      <c r="C14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="D14" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="F14" s="14"/>
-      <c r="G14" s="13" t="n">
+      <c r="F14" s="15"/>
+      <c r="G14" s="14" t="n">
         <v>27720</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B15" s="11" t="s">
+      <c r="A15" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="D15" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="F15" s="14"/>
-      <c r="G15" s="13" t="n">
+      <c r="F15" s="15"/>
+      <c r="G15" s="14" t="n">
         <v>154800</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B16" s="11" t="s">
+      <c r="A16" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B16" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="F16" s="14"/>
-      <c r="G16" s="13" t="n">
+      <c r="F16" s="15"/>
+      <c r="G16" s="14" t="n">
         <v>153000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B17" s="11" t="s">
+      <c r="A17" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B17" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D17" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F17" s="14"/>
-      <c r="G17" s="13" t="n">
+      <c r="F17" s="15"/>
+      <c r="G17" s="14" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="A18" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E18" s="18" t="s">
+      <c r="D18" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="F18" s="14" t="n">
         <v>1525.42</v>
       </c>
-      <c r="G18" s="14"/>
+      <c r="G18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B19" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="A19" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E19" s="18" t="s">
+      <c r="D19" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="14" t="n">
         <v>36610.17</v>
       </c>
-      <c r="G19" s="14"/>
+      <c r="G19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B20" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="A20" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E20" s="18" t="s">
+      <c r="D20" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E20" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="14" t="n">
         <v>113491.53</v>
       </c>
-      <c r="G20" s="14"/>
+      <c r="G20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="A21" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="D21" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E21" s="18" t="s">
+      <c r="D21" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="14" t="n">
         <v>34322.03</v>
       </c>
-      <c r="G21" s="14"/>
+      <c r="G21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="16" t="s">
+      <c r="A22" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E22" s="18" t="s">
+      <c r="D22" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="14" t="n">
         <v>5033.9</v>
       </c>
-      <c r="G22" s="14"/>
+      <c r="G22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B23" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="16" t="s">
+      <c r="A23" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="D23" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="18" t="s">
+      <c r="D23" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="F23" s="14" t="n">
         <v>1952.54</v>
       </c>
-      <c r="G23" s="14"/>
+      <c r="G23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B24" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="16" t="s">
+      <c r="A24" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E24" s="18" t="s">
+      <c r="D24" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E24" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="14" t="n">
         <v>381.36</v>
       </c>
-      <c r="G24" s="14"/>
+      <c r="G24" s="15"/>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B25" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="16" t="s">
+      <c r="A25" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="17" t="s">
+      <c r="D25" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="18" t="s">
+      <c r="E25" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="14" t="n">
         <v>152.46</v>
       </c>
-      <c r="G25" s="14"/>
+      <c r="G25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="16" t="s">
+      <c r="A26" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="17" t="s">
+      <c r="D26" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E26" s="18" t="s">
+      <c r="E26" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="14" t="n">
         <v>152.46</v>
       </c>
-      <c r="G26" s="14"/>
+      <c r="G26" s="15"/>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B27" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="A27" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D27" s="17" t="s">
+      <c r="D27" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E27" s="18" t="s">
+      <c r="E27" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="14" t="n">
         <v>1525.42</v>
       </c>
-      <c r="G27" s="14"/>
+      <c r="G27" s="15"/>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B28" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="16" t="s">
+      <c r="A28" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="13" t="n">
+      <c r="E28" s="19"/>
+      <c r="F28" s="14" t="n">
         <v>1800</v>
       </c>
-      <c r="G28" s="14"/>
+      <c r="G28" s="15"/>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B29" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="16" t="s">
+      <c r="A29" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E29" s="18" t="s">
+      <c r="D29" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E29" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="14" t="n">
         <v>1220.34</v>
       </c>
-      <c r="G29" s="14"/>
+      <c r="G29" s="15"/>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="16" t="s">
+      <c r="A30" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E30" s="18" t="s">
+      <c r="D30" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="14" t="n">
         <v>2181.36</v>
       </c>
-      <c r="G30" s="14"/>
+      <c r="G30" s="15"/>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="16" t="s">
+      <c r="A31" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E31" s="18" t="s">
+      <c r="D31" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E31" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="14" t="n">
         <v>6864.41</v>
       </c>
-      <c r="G31" s="14"/>
+      <c r="G31" s="15"/>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B32" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="16" t="s">
+      <c r="A32" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="D32" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="18" t="s">
+      <c r="D32" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="E32" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="14" t="n">
         <v>6864.41</v>
       </c>
-      <c r="G32" s="14"/>
+      <c r="G32" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -1870,32 +1874,32 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="2.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B1" s="11" t="s">
+      <c r="A1" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="13" t="n">
+      <c r="F1" s="15"/>
+      <c r="G1" s="14" t="n">
         <v>908010</v>
       </c>
     </row>
@@ -1918,32 +1922,32 @@
   <dimension ref="A1:G1"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="2.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="44.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="23.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="11.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="2.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="44.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="23.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="11.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="15" t="n">
-        <v>44593</v>
-      </c>
-      <c r="B1" s="11" t="s">
+      <c r="A1" s="16" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B1" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="13" t="n">
+      <c r="F1" s="15"/>
+      <c r="G1" s="14" t="n">
         <v>1000</v>
       </c>
     </row>
